--- a/WorkScripts/SynologyReader/Kostin_Georgii_template.xlsx
+++ b/WorkScripts/SynologyReader/Kostin_Georgii_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georgii.kostin\PycharmProjects\PythonProjects\WorkScripts\SynologyReader\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E121B240-130B-4E9E-A9FA-D370BC6A7E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE1A76A1-E3FA-4235-870B-03B7CB46C2DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29153" yWindow="1620" windowWidth="20507" windowHeight="12133" tabRatio="388" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3600" yWindow="2040" windowWidth="24300" windowHeight="12848" tabRatio="388" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks" sheetId="1" r:id="rId1"/>
@@ -1307,7 +1307,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.73046875" style="1" customWidth="1"/>
@@ -1450,89 +1450,173 @@
       <c r="E17" s="8"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="7"/>
       <c r="B19" s="11"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="8"/>
       <c r="E19" s="8"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="16"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="22"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="7"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="E22" s="8"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="B23" s="5"/>
-    </row>
-    <row r="24" spans="1:5" ht="14.65" thickBot="1"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="7"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+    </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="7"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="7"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="7"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="7"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="8"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="16"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="22"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="7"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="8"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="B35" s="5"/>
+    </row>
+    <row r="36" spans="1:5" ht="14.65" thickBot="1"/>
+    <row r="37" spans="1:5">
+      <c r="A37" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-    </row>
-    <row r="26" spans="1:5" ht="28.5">
-      <c r="A26" s="4" t="s">
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+    </row>
+    <row r="38" spans="1:5" ht="28.5">
+      <c r="A38" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B38" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C38" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="12"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="32" spans="1:5" ht="15" customHeight="1"/>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="12"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+    </row>
+    <row r="44" spans="1:5" ht="15" customHeight="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A33:E33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
